--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_topology_registry.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_topology_registry.xlsx
@@ -8,17 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadata" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nodes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="edges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="twin_pairs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="version_history" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evidence_summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="edges" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="twin_pairs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="version_history" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metadata'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'nodes'!$A$1:$M$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'edges'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'twin_pairs'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'version_history'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metadata'!$A$1:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'evidence_summary'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'nodes'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'edges'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'twin_pairs'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'version_history'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,20 +437,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="39" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,10 +508,45 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>research_confirmation_status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>research_confirmed_at</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>research_evidence_version</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>production_approval_status</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>maintenance_record_status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>topology_hash</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>research_topology_confirmed</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>production_topology_verified</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>topology_verified</t>
         </is>
@@ -511,27 +555,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7-topology-schema-v2.1</t>
+          <t>d7-topology-schema-v2.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_PROVIDED_RESEARCH_NOT_REQUIRED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>PENDING_PRODUCTION_APPROVAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>PENDING_PRODUCTION_APPROVAL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -551,20 +595,51 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>provisional_pending_field_verification</t>
+          <t>research_confirmed_production_pending</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
+          <t>author_confirmed</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-26T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>d7-topology-evidence-20260726</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>pending_documentary_audit_and_dual_approval</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>unavailable_not_required_for_research</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
+        </is>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:R2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -575,12 +650,491 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>author_confirmation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>process_line</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>author_confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>author_confirmation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>process_zone</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>author_confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>author_confirmation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>longitudinal_order</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>author_confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>author_confirmation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>scada_to_physical_point_one_to_one</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>author_confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>author_confirmation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>no_probe_or_channel_change_during_study</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>author_confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>instrument_inventory_DO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>listed_count</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>instrument_inventory_DO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>active_count</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>instrument_inventory_DO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>E+H</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>instrument_inventory_DO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0-20 mg/L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>instrument_inventory_DO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4-20 mA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>instrument_inventory_ORP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>listed_count</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>instrument_inventory_ORP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>active_count</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>instrument_inventory_ORP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>E+H</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>instrument_inventory_ORP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-1500 to 1500 mV</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>instrument_inventory_ORP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4-20 mA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>analyte_count_reconciled</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>inventory_limitation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>no_per_instrument_asset_or_device_code</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>inventory_limitation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no_serial_number</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inventory_limitation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no_explicit_line_zone_order_or_scada_mapping</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>inventory_limitation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>no_maintenance_or_replacement_history</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>research_use</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>eligible_for_ordinal_topology_reporting</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>production_governance</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pending_documentary_audit_and_dual_approval</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -589,7 +1143,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -668,12 +1222,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -716,7 +1270,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M2" t="b">
@@ -731,12 +1285,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -779,7 +1333,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M3" t="b">
@@ -794,12 +1348,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -842,7 +1396,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M4" t="b">
@@ -857,12 +1411,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -905,7 +1459,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M5" t="b">
@@ -920,12 +1474,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -968,7 +1522,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M6" t="b">
@@ -983,12 +1537,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1031,7 +1585,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M7" t="b">
@@ -1046,12 +1600,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1094,7 +1648,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M8" t="b">
@@ -1109,12 +1663,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1157,7 +1711,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M9" t="b">
@@ -1172,12 +1726,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1220,7 +1774,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M10" t="b">
@@ -1235,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1283,7 +1837,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M11" t="b">
@@ -1298,12 +1852,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1346,7 +1900,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M12" t="b">
@@ -1361,12 +1915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1409,7 +1963,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M13" t="b">
@@ -1424,12 +1978,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1472,7 +2026,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M14" t="b">
@@ -1487,12 +2041,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>NOT_AVAILABLE_IN_PROVIDED_REGISTER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1535,7 +2089,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>schematic_not_surveyed</t>
+          <t>schematic_ordinal_author_confirmed</t>
         </is>
       </c>
       <c r="M15" t="b">
@@ -1548,7 +2102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1939,7 +2493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2163,7 +2717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2172,11 +2726,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2209,27 +2763,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7-topology-declared-v1</t>
+          <t>d7-topology-author-confirmed-v2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>initial_declared_topology_pending_field_verification</t>
+          <t>author_confirmed_ordinal_topology_with_inventory_reconciliation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>PENDING_PRODUCTION_APPROVAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENDING_FIELD_VERIFICATION</t>
+          <t>PENDING_PRODUCTION_APPROVAL</t>
         </is>
       </c>
     </row>
